--- a/dcf/AMD.xlsx
+++ b/dcf/AMD.xlsx
@@ -864,7 +864,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1120,25 +1120,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.1383565499959667</v>
+        <v>0.1383589943156743</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.1433565499959668</v>
+        <v>0.1433589943156743</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.1483565499959668</v>
+        <v>0.1483589943156743</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1533565499959668</v>
+        <v>0.1533589943156743</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1583565499959668</v>
+        <v>0.1583589943156743</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1633565499959668</v>
+        <v>0.1633589943156743</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1683565499959668</v>
+        <v>0.1683589943156742</v>
       </c>
     </row>
     <row r="5">
@@ -1146,25 +1146,25 @@
         <v>12</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>145.1018208150584</v>
+        <v>111.3365145241839</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>140.0968655743204</v>
+        <v>107.6836362206489</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>135.3107273603221</v>
+        <v>104.1884585863738</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>130.7326660044743</v>
+        <v>100.8432847253689</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>126.3525183536937</v>
+        <v>97.64083003739727</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>122.160664769752</v>
+        <v>94.57419832189224</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>118.1479977132344</v>
+        <v>91.6368593672217</v>
       </c>
     </row>
     <row r="6">
@@ -1172,25 +1172,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>152.4276221069285</v>
+        <v>116.5399392423836</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>147.1085345007191</v>
+        <v>112.6639371296935</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>142.0230175448237</v>
+        <v>108.9561149560955</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>137.1595783790941</v>
+        <v>105.4082412015792</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>132.5073425826176</v>
+        <v>102.0125260643971</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>128.0560182283656</v>
+        <v>98.76159582856008</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>123.7958621763859</v>
+        <v>95.64846882601564</v>
       </c>
     </row>
     <row r="7">
@@ -1198,25 +1198,25 @@
         <v>14</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>159.7534233987987</v>
+        <v>121.7433639605834</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>154.1202034271179</v>
+        <v>117.6442380387381</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>148.7353077293253</v>
+        <v>113.7237713258172</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>143.5864907537139</v>
+        <v>109.9731976777896</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>138.6621668115415</v>
+        <v>106.384222091397</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>133.9513716869792</v>
+        <v>102.9489933352279</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>129.4437266395373</v>
+        <v>99.66007828480959</v>
       </c>
     </row>
     <row r="8">
@@ -1224,25 +1224,25 @@
         <v>15</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>167.0792246906689</v>
+        <v>126.9467886787832</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>161.1318723535166</v>
+        <v>122.6245389477826</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>155.4475979138269</v>
+        <v>118.4914276955389</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>150.0134031283337</v>
+        <v>114.538154154</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>144.8169910404653</v>
+        <v>110.7559181183969</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>139.8467251455928</v>
+        <v>107.1363908418958</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>135.0915911026888</v>
+        <v>103.6716877436035</v>
       </c>
     </row>
     <row r="9">
@@ -1250,25 +1250,25 @@
         <v>16</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>174.4050259825391</v>
+        <v>132.150213396983</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>168.1435412799154</v>
+        <v>127.6048398568272</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>162.1598880983285</v>
+        <v>123.2590840652606</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>156.4403155029534</v>
+        <v>119.1031106302103</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>150.9718152693892</v>
+        <v>115.1276141453968</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>145.7420786042065</v>
+        <v>111.3237883485636</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>140.7394555658403</v>
+        <v>107.6832972023975</v>
       </c>
     </row>
     <row r="10">
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>181.7308272744093</v>
+        <v>137.3536381151827</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>175.1552102063141</v>
+        <v>132.5851407658718</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>168.8721782828301</v>
+        <v>128.0267404349822</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>162.8672278775732</v>
+        <v>123.6680671064207</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>157.126639498313</v>
+        <v>119.4993101723967</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>151.63743206282</v>
+        <v>115.5111858552315</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>146.3873200289917</v>
+        <v>111.6949066611914</v>
       </c>
     </row>
     <row r="11">
@@ -1302,25 +1302,25 @@
         <v>18</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>189.0566285662794</v>
+        <v>142.5570628333825</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>182.1668791327128</v>
+        <v>137.5654416749163</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>175.5844684673317</v>
+        <v>132.7943968047039</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>169.294140252193</v>
+        <v>128.233023582631</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>163.2814637272369</v>
+        <v>123.8710061993965</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>157.5327855214337</v>
+        <v>119.6985833618993</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>152.0351844921432</v>
+        <v>115.7065161199854</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>517.8200073242188</v>
+        <v>520.9849853515625</v>
       </c>
     </row>
     <row r="14">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1533565499959668</v>
+        <v>0.1533589943156743</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>15</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.013413269222249</v>
+        <v>1.031704855275506</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24457,7 +24457,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>517.8200073242188</v>
+        <v>520.9849853515625</v>
       </c>
     </row>
     <row r="49">
@@ -24467,7 +24467,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24619,13 +24619,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>150.0134031283337</v>
+        <v>114.538154154</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>200.5523338413206</v>
+        <v>149.0407632135271</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>111.3990391908296</v>
+        <v>87.5230501295156</v>
       </c>
     </row>
     <row r="59">
